--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484250_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484250_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.842</v>
+        <v>3.0423</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6379</v>
+        <v>0.5241</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4799</v>
+        <v>2.5183</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0936</v>
+        <v>0.7804</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09520000000000001</v>
+        <v>2.021</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9984</v>
+        <v>-1.2406</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.022</v>
+        <v>-0.2083</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7547</v>
+        <v>1.1665</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.2673</v>
+        <v>-1.3748</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9284</v>
+        <v>0.9887</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6595</v>
+        <v>0.8545</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2688</v>
+        <v>0.1342</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1542</v>
+        <v>0.2386</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5794</v>
+        <v>0.0765</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5748</v>
+        <v>0.1622</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7873</v>
+        <v>2.1694</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5675</v>
+        <v>0.7439</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3549</v>
+        <v>1.4255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7804</v>
+        <v>0.8807</v>
       </c>
       <c r="H3" t="n">
-        <v>2.021</v>
+        <v>1.0161</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2406</v>
+        <v>-0.1354</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2083</v>
+        <v>0.3517</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1665</v>
+        <v>0.3517</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3748</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9887</v>
+        <v>0.529</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8545</v>
+        <v>0.6644</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1342</v>
+        <v>-0.1354</v>
       </c>
       <c r="P3" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0164</v>
+        <v>0.4292</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0151</v>
+        <v>0.5875</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0013</v>
+        <v>-0.1583</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8279</v>
+        <v>0.6642</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2487</v>
+        <v>1.5211</v>
       </c>
       <c r="E4" t="n">
         <v>2.8305</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5818</v>
+        <v>-1.3095</v>
       </c>
       <c r="G4" t="n">
         <v>3.0964</v>
@@ -766,13 +766,13 @@
         <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6328</v>
+        <v>-0.3604</v>
       </c>
       <c r="T4" t="n">
         <v>0.2312</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.864</v>
+        <v>-0.5917</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6056</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1481</v>
+        <v>1.264</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0767</v>
+        <v>-1.8335</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0715</v>
+        <v>3.0975</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8807</v>
+        <v>1.1491</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0161</v>
+        <v>0.0568</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1354</v>
+        <v>1.0924</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3517</v>
+        <v>-0.5234</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3517</v>
+        <v>-1.0771</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.5537</v>
       </c>
       <c r="M5" t="n">
-        <v>0.529</v>
+        <v>1.6725</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6644</v>
+        <v>1.1338</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1354</v>
+        <v>0.5387</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5921</v>
+        <v>0.8143</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.5614</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5124</v>
+        <v>0.2529</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1555</v>
+        <v>-1.2851</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1379</v>
+        <v>1.9351</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6158</v>
+        <v>-1.0936</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2505</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.9984</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6227</v>
+        <v>-2.022</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2563</v>
+        <v>-0.7547</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2673</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9932</v>
+        <v>0.9284</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9942</v>
+        <v>0.6595</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001</v>
+        <v>0.2688</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>3.066</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0114</v>
+        <v>0.9322</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0546</v>
+        <v>0.03</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>F. REYES ARANDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.908</v>
+        <v>-0.1854</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2985</v>
+        <v>-0.3226</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2065</v>
+        <v>0.1371</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1491</v>
+        <v>0.1888</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0568</v>
+        <v>-0.8631</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0924</v>
+        <v>1.0519</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5234</v>
+        <v>-0.0062</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0771</v>
+        <v>-0.6536</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5537</v>
+        <v>0.6475</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6725</v>
+        <v>0.1949</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1338</v>
+        <v>-0.2095</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5387</v>
+        <v>0.4045</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4583</v>
+        <v>-0.5695</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0964</v>
+        <v>-0.121</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3619</v>
+        <v>-0.4485</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.194</v>
+        <v>-0.4768</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6582</v>
+        <v>-4.4988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8522</v>
+        <v>4.022</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2249</v>
+        <v>-1.0261</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8445</v>
+        <v>-0.4321</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6196</v>
+        <v>-0.594</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.265</v>
+        <v>-2.549</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.3459</v>
+        <v>-1.2817</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>-1.2673</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0401</v>
+        <v>1.5229</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4986</v>
+        <v>0.8496</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5387</v>
+        <v>0.6733</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8095</v>
+        <v>0.4711</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5602</v>
+        <v>0.199</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7507</v>
+        <v>0.2721</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. REYES ARANDA</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2399</v>
+        <v>-0.5203</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3226</v>
+        <v>-1.0862</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0827</v>
+        <v>0.5659</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1888</v>
+        <v>2.6158</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8631</v>
+        <v>3.2505</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0519</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0062</v>
+        <v>1.6227</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6536</v>
+        <v>2.2563</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6475</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1949</v>
+        <v>0.9932</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2095</v>
+        <v>0.9942</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4045</v>
+        <v>-0.001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.624</v>
+        <v>1.5634</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>1.0808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.503</v>
+        <v>0.4826</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4751</v>
+        <v>-0.9705</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3881</v>
+        <v>-2.0133</v>
       </c>
       <c r="F10" t="n">
-        <v>3.913</v>
+        <v>1.0428</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0261</v>
+        <v>-2.2249</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4321</v>
+        <v>-2.8445</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.594</v>
+        <v>0.6196</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.549</v>
+        <v>-2.265</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2817</v>
+        <v>-2.3459</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2673</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5229</v>
+        <v>0.0401</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8496</v>
+        <v>-0.4986</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6733</v>
+        <v>0.5387</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5272</v>
+        <v>-0.3549</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6904</v>
+        <v>0.2052</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1632</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.449</v>
+        <v>-2.6863</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.706</v>
+        <v>-1.0794</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7431</v>
+        <v>-1.6069</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4673</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5325</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9408</v>
+        <v>-0.3142</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5917</v>
+        <v>-0.4555</v>
       </c>
       <c r="V11" t="n">
         <v>0.9414</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6387</v>
+        <v>-3.5921</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0536</v>
+        <v>-1.9525</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5851</v>
+        <v>-1.6396</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4814</v>
@@ -1390,13 +1390,13 @@
         <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3527</v>
+        <v>-0.3061</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1315</v>
+        <v>0.077</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2186</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6922000000000006</v>
+        <v>0.2154000000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.8807</v>
+        <v>-9.972900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1886</v>
+        <v>10.1882</v>
       </c>
       <c r="G13" t="n">
         <v>0.4179000000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>1.770199999999999</v>
+        <v>1.7702</v>
       </c>
       <c r="I13" t="n">
         <v>-1.3521</v>
@@ -1444,13 +1444,13 @@
         <v>-4.0996</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.732</v>
+        <v>-0.7319999999999998</v>
       </c>
       <c r="L13" t="n">
         <v>-3.3675</v>
       </c>
       <c r="M13" t="n">
-        <v>4.517499999999999</v>
+        <v>4.5175</v>
       </c>
       <c r="N13" t="n">
         <v>2.5023</v>
@@ -1465,19 +1465,19 @@
         <v>-12.6973</v>
       </c>
       <c r="R13" t="n">
-        <v>9.767100000000001</v>
+        <v>9.767099999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.210299999999999</v>
+        <v>2.1182</v>
       </c>
       <c r="T13" t="n">
-        <v>2.147400000000001</v>
+        <v>3.0555</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9370999999999998</v>
+        <v>-0.9372000000000003</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6093000000000002</v>
+        <v>0.6093000000000004</v>
       </c>
       <c r="W13" t="n">
         <v>3.7685</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. MAYO SCHWANDT</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7445</v>
+        <v>4.4034</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7494</v>
+        <v>3.5523</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9951</v>
+        <v>0.8511</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9596</v>
+        <v>0.7046</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8923</v>
+        <v>0.5958</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0673</v>
+        <v>0.1088</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4545</v>
+        <v>0.674</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9263</v>
+        <v>0.6996</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4718</v>
+        <v>-0.0257</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5051</v>
+        <v>0.0306</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.034</v>
+        <v>-0.1038</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5391</v>
+        <v>0.1344</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0119</v>
+        <v>1.0393</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2949</v>
+        <v>0.4411</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.283</v>
+        <v>0.5982</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3991</v>
+        <v>1.0968</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3991</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>I. MAYO SCHWANDT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9666</v>
+        <v>3.6867</v>
       </c>
       <c r="E15" t="n">
-        <v>3.249</v>
+        <v>2.2327</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7176</v>
+        <v>1.454</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7046</v>
+        <v>1.9596</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5958</v>
+        <v>1.8923</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1088</v>
+        <v>0.0673</v>
       </c>
       <c r="J15" t="n">
-        <v>0.674</v>
+        <v>1.4545</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6996</v>
+        <v>1.9263</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0257</v>
+        <v>-0.4718</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0306</v>
+        <v>0.5051</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1038</v>
+        <v>-0.034</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1344</v>
+        <v>0.5391</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6025</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1377</v>
+        <v>0.7781</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4648</v>
+        <v>0.1759</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0968</v>
+        <v>-0.3991</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3405</v>
+        <v>-0.3991</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5069</v>
+        <v>2.8071</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1047</v>
+        <v>2.217</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4022</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>1.0101</v>
@@ -1702,13 +1702,13 @@
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0725</v>
+        <v>0.2277</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2105</v>
+        <v>-0.0982</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1379</v>
+        <v>0.3259</v>
       </c>
       <c r="V16" t="n">
         <v>1.374</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7197</v>
+        <v>0.8661</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2698</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9895</v>
+        <v>0.9336</v>
       </c>
       <c r="G17" t="n">
         <v>1.3998</v>
@@ -1780,13 +1780,13 @@
         <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2895</v>
+        <v>-0.1431</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2283</v>
+        <v>-0.0261</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0612</v>
+        <v>-0.117</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6619</v>
+        <v>0.7532</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1708</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4911</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5571</v>
+        <v>0.2951</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1967</v>
+        <v>0.012</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7538</v>
+        <v>0.2831</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2569</v>
+        <v>0.4449</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9581</v>
+        <v>-0.243</v>
       </c>
       <c r="L18" t="n">
-        <v>1.215</v>
+        <v>0.6879</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3002</v>
+        <v>-0.1498</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2386</v>
+        <v>0.2551</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5389</v>
+        <v>-0.4049</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4369</v>
+        <v>0.9939</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5315</v>
+        <v>0.4327</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0946</v>
+        <v>0.5612</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>-0.7312</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2864</v>
+        <v>0.2012</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4025</v>
+        <v>-0.1406</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6889</v>
+        <v>0.3418</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2951</v>
+        <v>0.1709</v>
       </c>
       <c r="H19" t="n">
-        <v>0.012</v>
+        <v>-0.0987</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2831</v>
+        <v>0.2696</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4449</v>
+        <v>0.0409</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.243</v>
+        <v>0.0409</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1498</v>
+        <v>0.13</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2551</v>
+        <v>-0.1397</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4049</v>
+        <v>0.2696</v>
       </c>
       <c r="P19" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5272</v>
+        <v>-0.1651</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1294</v>
+        <v>-0.1816</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3978</v>
+        <v>0.0165</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7312</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1467</v>
+        <v>-0.0163</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1406</v>
+        <v>-1.8915</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2873</v>
+        <v>1.8752</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1709</v>
+        <v>-0.766</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0987</v>
+        <v>-2.0609</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2696</v>
+        <v>1.2949</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0409</v>
+        <v>-2.0347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0409</v>
+        <v>-2.6555</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6208</v>
       </c>
       <c r="M20" t="n">
-        <v>0.13</v>
+        <v>1.2687</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1397</v>
+        <v>0.5946</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2696</v>
+        <v>0.6741</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2196</v>
+        <v>-0.0316</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1816</v>
+        <v>0.1432</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.038</v>
+        <v>-0.1748</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3676</v>
+        <v>-0.0786</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8915</v>
+        <v>-1.1759</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5239</v>
+        <v>1.0973</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.766</v>
+        <v>0.083</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0609</v>
+        <v>-0.537</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2949</v>
+        <v>0.62</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0347</v>
+        <v>-0.5714</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6555</v>
+        <v>-0.6524</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6208</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2687</v>
+        <v>0.6545</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5946</v>
+        <v>0.1154</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6741</v>
+        <v>0.5391</v>
       </c>
       <c r="P21" t="n">
         <v>0.7814</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.383</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1432</v>
+        <v>-0.6045</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5261</v>
+        <v>-0.3385</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8436</v>
+        <v>-0.6641</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4793</v>
+        <v>-1.7504</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6357</v>
+        <v>1.0862</v>
       </c>
       <c r="G22" t="n">
-        <v>0.083</v>
+        <v>0.5571</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.537</v>
+        <v>-1.1967</v>
       </c>
       <c r="I22" t="n">
-        <v>0.62</v>
+        <v>1.7538</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5714</v>
+        <v>0.2569</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6524</v>
+        <v>-0.9581</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0809</v>
+        <v>1.215</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6545</v>
+        <v>0.3002</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1154</v>
+        <v>-0.2386</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5391</v>
+        <v>0.5389</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.708</v>
+        <v>0.1108</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.6103</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8002</v>
+        <v>-0.4995</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2229</v>
+        <v>-2.3135</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8145</v>
+        <v>-5.3847</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5916</v>
+        <v>3.0712</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.935</v>
+        <v>-2.5799</v>
       </c>
       <c r="H23" t="n">
-        <v>0.166</v>
+        <v>0.319</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1011</v>
+        <v>-2.8989</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.3897</v>
+        <v>-2.8152</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0192</v>
+        <v>0.353</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.3705</v>
+        <v>-3.1682</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4547</v>
+        <v>0.2353</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1852</v>
+        <v>-0.034</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2694</v>
+        <v>0.2692</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0693</v>
+        <v>0.8329</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5752</v>
+        <v>0.0834</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6445</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.9962</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2869</v>
+        <v>-2.6145</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.497</v>
+        <v>-3.4212</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2101</v>
+        <v>0.8068</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5799</v>
+        <v>-2.935</v>
       </c>
       <c r="H24" t="n">
-        <v>0.319</v>
+        <v>0.166</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.8989</v>
+        <v>-3.1011</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8152</v>
+        <v>-3.3897</v>
       </c>
       <c r="K24" t="n">
-        <v>0.353</v>
+        <v>-0.0192</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.1682</v>
+        <v>-3.3705</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2353</v>
+        <v>0.4547</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.034</v>
+        <v>0.1852</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2692</v>
+        <v>0.2694</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1405</v>
+        <v>-0.4608</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0289</v>
+        <v>-0.0315</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8884</v>
+        <v>-0.4293</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9962</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.719</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6195</v>
+        <v>-3.642</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9672</v>
+        <v>-4.2594</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3477</v>
+        <v>0.6173</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3174</v>
@@ -2404,13 +2404,13 @@
         <v>1.5627</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9067</v>
+        <v>-0.9292</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3177</v>
+        <v>-0.6099</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.589</v>
+        <v>-0.3193</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0047</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.692199999999997</v>
+        <v>3.388700000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.1885</v>
+        <v>-10.1884</v>
       </c>
       <c r="F26" t="n">
-        <v>10.8807</v>
+        <v>13.577</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4180999999999998</v>
+        <v>-0.4181000000000007</v>
       </c>
       <c r="H26" t="n">
         <v>-1.7702</v>
@@ -2455,7 +2455,7 @@
         <v>1.3521</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.5176</v>
+        <v>-4.517600000000001</v>
       </c>
       <c r="K26" t="n">
         <v>-2.5023</v>
@@ -2467,7 +2467,7 @@
         <v>4.0996</v>
       </c>
       <c r="N26" t="n">
-        <v>0.732</v>
+        <v>0.7319999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>3.3674</v>
@@ -2482,16 +2482,16 @@
         <v>12.6973</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2106</v>
+        <v>1.4859</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9371000000000003</v>
+        <v>0.9369999999999997</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.1477</v>
+        <v>0.5488000000000002</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6094000000000004</v>
+        <v>-0.6094000000000002</v>
       </c>
       <c r="W26" t="n">
         <v>3.1592</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484250_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484250_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0423</v>
+        <v>2.1694</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5241</v>
+        <v>0.7439</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5183</v>
+        <v>1.4255</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7804</v>
+        <v>0.8807</v>
       </c>
       <c r="H2" t="n">
-        <v>2.021</v>
+        <v>1.0161</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2406</v>
+        <v>-0.1354</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2083</v>
+        <v>0.3517</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1665</v>
+        <v>0.3517</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.3748</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9887</v>
+        <v>0.529</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8545</v>
+        <v>0.6644</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1342</v>
+        <v>-0.1354</v>
       </c>
       <c r="P2" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2386</v>
+        <v>0.4292</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0765</v>
+        <v>0.5875</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1622</v>
+        <v>-0.1583</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8279</v>
+        <v>0.6642</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +653,72 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1694</v>
+        <v>1.5279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7439</v>
+        <v>1.5279</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4255</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8807</v>
+        <v>1.5279</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0161</v>
+        <v>0.921</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1354</v>
+        <v>0.607</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3517</v>
+        <v>1.5279</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3517</v>
+        <v>0.921</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M3" t="n">
-        <v>0.529</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6644</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4292</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.264</v>
+        <v>1.5144</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8335</v>
+        <v>-1.0039</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0975</v>
+        <v>2.5183</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1491</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0568</v>
+        <v>1.1001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0924</v>
+        <v>-1.8476</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5234</v>
+        <v>-1.7362</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0771</v>
+        <v>0.2456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5537</v>
+        <v>-1.9818</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6725</v>
+        <v>0.9887</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1338</v>
+        <v>0.8545</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5387</v>
+        <v>0.1342</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8143</v>
+        <v>0.2386</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5614</v>
+        <v>0.0765</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2529</v>
+        <v>0.1622</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2772</v>
+        <v>1.8279</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>1.8279</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65</v>
+        <v>1.264</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2851</v>
+        <v>-1.8335</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9351</v>
+        <v>3.0975</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0936</v>
+        <v>1.1491</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.0568</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9984</v>
+        <v>1.0924</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.022</v>
+        <v>-0.5234</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7547</v>
+        <v>-1.0771</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2673</v>
+        <v>0.5537</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9284</v>
+        <v>1.6725</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6595</v>
+        <v>1.1338</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2688</v>
+        <v>0.5387</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.8143</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9322</v>
+        <v>0.5614</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03</v>
+        <v>0.2529</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. REYES ARANDA</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1854</v>
+        <v>0.65</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3226</v>
+        <v>-1.2851</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1371</v>
+        <v>1.9351</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1888</v>
+        <v>-1.0936</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8631</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0519</v>
+        <v>-0.9984</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0062</v>
+        <v>-2.022</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6536</v>
+        <v>-0.7547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6475</v>
+        <v>-1.2673</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1949</v>
+        <v>0.9284</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2095</v>
+        <v>0.6595</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4045</v>
+        <v>0.2688</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5695</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.121</v>
+        <v>0.9322</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4485</v>
+        <v>0.03</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>F. REYES ARANDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4768</v>
+        <v>-0.1854</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.4988</v>
+        <v>-0.3226</v>
       </c>
       <c r="F8" t="n">
-        <v>4.022</v>
+        <v>0.1371</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0261</v>
+        <v>0.1888</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4321</v>
+        <v>-0.8631</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.594</v>
+        <v>1.0519</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.549</v>
+        <v>-0.0062</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2817</v>
+        <v>-0.6536</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2673</v>
+        <v>0.6475</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5229</v>
+        <v>0.1949</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8496</v>
+        <v>-0.2095</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6733</v>
+        <v>0.4045</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4711</v>
+        <v>-0.5695</v>
       </c>
       <c r="T8" t="n">
-        <v>0.199</v>
+        <v>-0.121</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2721</v>
+        <v>-0.4485</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5203</v>
+        <v>-0.4768</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0862</v>
+        <v>-4.4988</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5659</v>
+        <v>4.022</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6158</v>
+        <v>-1.0261</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2505</v>
+        <v>-0.4321</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.594</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6227</v>
+        <v>-2.549</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2563</v>
+        <v>-1.2817</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2673</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9932</v>
+        <v>1.5229</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9942</v>
+        <v>0.8496</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.001</v>
+        <v>0.6733</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5395</v>
+        <v>-0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5634</v>
+        <v>0.4711</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0808</v>
+        <v>0.199</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4826</v>
+        <v>0.2721</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.16</v>
+        <v>0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9705</v>
+        <v>-0.5203</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0133</v>
+        <v>-1.0862</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0428</v>
+        <v>0.5659</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2249</v>
+        <v>2.6158</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8445</v>
+        <v>3.2505</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6196</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.265</v>
+        <v>1.6227</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3459</v>
+        <v>2.2563</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0401</v>
+        <v>0.9932</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4986</v>
+        <v>0.9942</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5387</v>
+        <v>-0.001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3549</v>
+        <v>1.5634</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2052</v>
+        <v>1.0808</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.4826</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2186</v>
+        <v>-2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6863</v>
+        <v>-0.9705</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0794</v>
+        <v>-2.0133</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6069</v>
+        <v>1.0428</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4673</v>
+        <v>-2.2249</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4851</v>
+        <v>-2.8445</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9822</v>
+        <v>0.6196</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.089</v>
+        <v>-2.265</v>
       </c>
       <c r="K11" t="n">
-        <v>0.353</v>
+        <v>-2.3459</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.442</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3783</v>
+        <v>0.0401</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.838</v>
+        <v>-0.4986</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5403</v>
+        <v>0.5387</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.3549</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3142</v>
+        <v>0.2052</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4555</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9414</v>
+        <v>1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5921</v>
+        <v>-2.6863</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9525</v>
+        <v>-1.0794</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6396</v>
+        <v>-1.6069</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4814</v>
+        <v>-2.4673</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3868</v>
+        <v>-0.4851</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0946</v>
+        <v>-1.9822</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5927</v>
+        <v>-1.089</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6332</v>
+        <v>0.353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0405</v>
+        <v>-1.442</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8887</v>
+        <v>-1.3783</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7536</v>
+        <v>-0.838</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.135</v>
+        <v>-0.5403</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3061</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3831</v>
+        <v>-0.3142</v>
       </c>
       <c r="U12" t="n">
-        <v>0.077</v>
+        <v>-0.4555</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2186</v>
+        <v>0.9414</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2154000000000003</v>
+        <v>-3.5921</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.972900000000001</v>
+        <v>-1.9525</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1882</v>
+        <v>-1.6396</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4179000000000002</v>
+        <v>-1.4814</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7702</v>
+        <v>-1.3868</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3521</v>
+        <v>-0.0946</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.0996</v>
+        <v>-0.5927</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7319999999999998</v>
+        <v>-0.6332</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.3675</v>
+        <v>0.0405</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5175</v>
+        <v>-0.8887</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5023</v>
+        <v>-0.7536</v>
       </c>
       <c r="O13" t="n">
-        <v>2.0153</v>
+        <v>-0.135</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9302</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6973</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>9.767099999999999</v>
+        <v>0.3907</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1182</v>
+        <v>-0.3061</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0555</v>
+        <v>-0.3831</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9372000000000003</v>
+        <v>0.077</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6093000000000004</v>
+        <v>-1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1592</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4034</v>
+        <v>0.2154000000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5523</v>
+        <v>-9.973000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8511</v>
+        <v>10.1882</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7046</v>
+        <v>0.4179000000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5958</v>
+        <v>1.770300000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1088</v>
+        <v>-1.3521</v>
       </c>
       <c r="J14" t="n">
-        <v>0.674</v>
+        <v>-4.0996</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6996</v>
+        <v>-0.7319000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0257</v>
+        <v>-3.3675</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0306</v>
+        <v>4.517499999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1038</v>
+        <v>2.5023</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1344</v>
+        <v>2.0153</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>-2.9302</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-12.6973</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>9.767099999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0393</v>
+        <v>2.1182</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4411</v>
+        <v>3.0555</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5982</v>
+        <v>-0.9372</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0968</v>
+        <v>0.6093</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4373</v>
+        <v>3.7685</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3405</v>
-      </c>
+        <v>-3.1592</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. MAYO SCHWANDT</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6867</v>
+        <v>4.4034</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2327</v>
+        <v>3.5523</v>
       </c>
       <c r="F15" t="n">
-        <v>1.454</v>
+        <v>0.8511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9596</v>
+        <v>0.7046</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8923</v>
+        <v>0.5958</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0673</v>
+        <v>0.1088</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4545</v>
+        <v>0.674</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9263</v>
+        <v>0.6996</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4718</v>
+        <v>-0.0257</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5051</v>
+        <v>0.0306</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.034</v>
+        <v>-0.1038</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5391</v>
+        <v>0.1344</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.0393</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7781</v>
+        <v>0.4411</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1759</v>
+        <v>0.5982</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3991</v>
+        <v>1.0968</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3991</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>I. MAYO SCHWANDT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8071</v>
+        <v>3.6867</v>
       </c>
       <c r="E16" t="n">
-        <v>2.217</v>
+        <v>2.2327</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5901999999999999</v>
+        <v>1.454</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0101</v>
+        <v>1.9596</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0025</v>
+        <v>1.8923</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0126</v>
+        <v>0.0673</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5188</v>
+        <v>1.4545</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3709</v>
+        <v>1.9263</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1478</v>
+        <v>-0.4718</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5087</v>
+        <v>0.5051</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3735</v>
+        <v>-0.034</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1352</v>
+        <v>0.5391</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2277</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0982</v>
+        <v>0.7781</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3259</v>
+        <v>0.1759</v>
       </c>
       <c r="V16" t="n">
-        <v>1.374</v>
+        <v>-0.3991</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.3991</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8661</v>
+        <v>2.8071</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06759999999999999</v>
+        <v>2.217</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9336</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3998</v>
+        <v>1.0101</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6176</v>
+        <v>-0.0025</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7823</v>
+        <v>1.0126</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9352</v>
+        <v>1.5188</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2878</v>
+        <v>0.3709</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6475</v>
+        <v>1.1478</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4646</v>
+        <v>-0.5087</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3298</v>
+        <v>-0.3735</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1348</v>
+        <v>-0.1352</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1431</v>
+        <v>0.2277</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0261</v>
+        <v>-0.0982</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.117</v>
+        <v>0.3259</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.374</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7532</v>
+        <v>0.921</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8522999999999999</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2951</v>
+        <v>0.921</v>
       </c>
       <c r="H18" t="n">
-        <v>0.012</v>
+        <v>0.921</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4449</v>
+        <v>0.921</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.243</v>
+        <v>0.921</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1498</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2551</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4049</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9939</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4327</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5612</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7312</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7312</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2012</v>
+        <v>0.8661</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1406</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3418</v>
+        <v>0.9336</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1709</v>
+        <v>1.3998</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0987</v>
+        <v>0.6176</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2696</v>
+        <v>0.7823</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0409</v>
+        <v>0.9352</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0409</v>
+        <v>0.2878</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.6475</v>
       </c>
       <c r="M19" t="n">
-        <v>0.13</v>
+        <v>0.4646</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1397</v>
+        <v>0.3298</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>0.1348</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1651</v>
+        <v>-0.1431</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1816</v>
+        <v>-0.0261</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0165</v>
+        <v>-0.117</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0163</v>
+        <v>0.7532</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8915</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8752</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.766</v>
+        <v>0.2951</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0609</v>
+        <v>0.012</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2949</v>
+        <v>0.2831</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0347</v>
+        <v>0.4449</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.6555</v>
+        <v>-0.243</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6208</v>
+        <v>0.6879</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2687</v>
+        <v>-0.1498</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5946</v>
+        <v>0.2551</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6741</v>
+        <v>-0.4049</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0316</v>
+        <v>0.9939</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1432</v>
+        <v>0.4327</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1748</v>
+        <v>0.5612</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.7312</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.7312</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0786</v>
+        <v>0.2012</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1759</v>
+        <v>-0.1406</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0973</v>
+        <v>0.3418</v>
       </c>
       <c r="G21" t="n">
-        <v>0.083</v>
+        <v>0.1709</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.537</v>
+        <v>-0.0987</v>
       </c>
       <c r="I21" t="n">
-        <v>0.62</v>
+        <v>0.2696</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5714</v>
+        <v>0.0409</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6524</v>
+        <v>0.0409</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6545</v>
+        <v>0.13</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1154</v>
+        <v>-0.1397</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5391</v>
+        <v>0.2696</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.1651</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6045</v>
+        <v>-0.1816</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3385</v>
+        <v>0.0165</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6641</v>
+        <v>-0.0163</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7504</v>
+        <v>-1.8915</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0862</v>
+        <v>1.8752</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5571</v>
+        <v>-0.766</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1967</v>
+        <v>-2.0609</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7538</v>
+        <v>1.2949</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2569</v>
+        <v>-2.0347</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9581</v>
+        <v>-2.6555</v>
       </c>
       <c r="L22" t="n">
-        <v>1.215</v>
+        <v>0.6208</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3002</v>
+        <v>1.2687</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2386</v>
+        <v>0.5946</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5389</v>
+        <v>0.6741</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1108</v>
+        <v>-0.0316</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6103</v>
+        <v>0.1432</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4995</v>
+        <v>-0.1748</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3135</v>
+        <v>-0.0786</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3847</v>
+        <v>-1.1759</v>
       </c>
       <c r="F23" t="n">
-        <v>3.0712</v>
+        <v>1.0973</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5799</v>
+        <v>0.083</v>
       </c>
       <c r="H23" t="n">
-        <v>0.319</v>
+        <v>-0.537</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8989</v>
+        <v>0.62</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.8152</v>
+        <v>-0.5714</v>
       </c>
       <c r="K23" t="n">
-        <v>0.353</v>
+        <v>-0.6524</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.1682</v>
+        <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2353</v>
+        <v>0.6545</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.034</v>
+        <v>0.1154</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2692</v>
+        <v>0.5391</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8329</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0834</v>
+        <v>-0.6045</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7495000000000001</v>
+        <v>-0.3385</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9962</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.719</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6145</v>
+        <v>-0.6641</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4212</v>
+        <v>-1.7504</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8068</v>
+        <v>1.0862</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.935</v>
+        <v>0.5571</v>
       </c>
       <c r="H24" t="n">
-        <v>0.166</v>
+        <v>-1.1967</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.1011</v>
+        <v>1.7538</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.3897</v>
+        <v>0.2569</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0192</v>
+        <v>-0.9581</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.3705</v>
+        <v>1.215</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4547</v>
+        <v>0.3002</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1852</v>
+        <v>-0.2386</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2694</v>
+        <v>0.5389</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4608</v>
+        <v>0.1108</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0315</v>
+        <v>0.6103</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4293</v>
+        <v>-0.4995</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.642</v>
+        <v>-2.6145</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2594</v>
+        <v>-3.4212</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6173</v>
+        <v>0.8068</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3174</v>
+        <v>-2.935</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4771</v>
+        <v>0.166</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1597</v>
+        <v>-3.1011</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0318</v>
+        <v>-3.3897</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6526</v>
+        <v>-0.0192</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6208</v>
+        <v>-3.3705</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7144</v>
+        <v>0.4547</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1755</v>
+        <v>0.1852</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5389</v>
+        <v>0.2694</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9292</v>
+        <v>-0.4608</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6099</v>
+        <v>-0.0315</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3193</v>
+        <v>-0.4293</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.0047</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.388700000000001</v>
+        <v>-3.2344</v>
       </c>
       <c r="E26" t="n">
+        <v>-6.3057</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.0712</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.5009</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.6019</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.8989</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-3.7361</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.5679999999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-3.1682</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.8329</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. SAMAKE EL ALAOUI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.642</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.2594</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.3174</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.4771</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.1597</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.0318</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.6526</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7144</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.9292</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.6099</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.3193</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-2.0047</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.3405</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484250_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.388800000000002</v>
+      </c>
+      <c r="E28" t="n">
         <v>-10.1884</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>13.577</v>
       </c>
-      <c r="G26" t="n">
-        <v>-0.4181000000000007</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-1.7702</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="G28" t="n">
+        <v>-0.4180999999999998</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.7701</v>
+      </c>
+      <c r="I28" t="n">
         <v>1.3521</v>
       </c>
-      <c r="J26" t="n">
-        <v>-4.517600000000001</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J28" t="n">
+        <v>-4.5175</v>
+      </c>
+      <c r="K28" t="n">
         <v>-2.5023</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L28" t="n">
         <v>-2.0155</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>4.0996</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.7319999999999999</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="N28" t="n">
+        <v>0.7320000000000001</v>
+      </c>
+      <c r="O28" t="n">
         <v>3.3674</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>2.9301</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-9.766999999999999</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>1.4859</v>
       </c>
-      <c r="T26" t="n">
-        <v>0.9369999999999997</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="T28" t="n">
+        <v>0.9369999999999995</v>
+      </c>
+      <c r="U28" t="n">
         <v>0.5488000000000002</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V28" t="n">
         <v>-0.6094000000000002</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>3.1592</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>-3.7686</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
